--- a/pachislot-db/output/slot_machine_database.xlsx
+++ b/pachislot-db/output/slot_machine_database.xlsx
@@ -1,53 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="機種マスター" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="出率ランキング" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="要確認" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="未取得機種" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="機種マスター" sheetId="1" r:id="rId1"/>
+    <sheet name="出率ランキング" sheetId="2" r:id="rId2"/>
+    <sheet name="要確認" sheetId="3" r:id="rId3"/>
+    <sheet name="未取得機種" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'機種マスター'!$A$1:$Y$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'出率ランキング'!$A$1:$E$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'要確認'!$A$1:$G$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'未取得機種'!$A$1:$F$4</definedName>
-  </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="FF1F3864"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,2622 +54,2111 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="60" customWidth="1" min="18" max="18"/>
-    <col width="60" customWidth="1" min="19" max="19"/>
-    <col width="60" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="60" customWidth="1" min="24" max="24"/>
-    <col width="31" customWidth="1" min="25" max="25"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="55" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="11" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="16" max="16" width="11" customWidth="1"/>
+    <col min="17" max="17" width="24" customWidth="1"/>
+    <col min="18" max="18" width="60" customWidth="1"/>
+    <col min="19" max="19" width="60" customWidth="1"/>
+    <col min="20" max="20" width="60" customWidth="1"/>
+    <col min="21" max="21" width="14" customWidth="1"/>
+    <col min="22" max="22" width="16" customWidth="1"/>
+    <col min="23" max="23" width="10" customWidth="1"/>
+    <col min="24" max="24" width="60" customWidth="1"/>
+    <col min="25" max="25" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>機種名</t>
+          <t xml:space="preserve">機種名</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>メーカー</t>
+          <t xml:space="preserve">メーカー</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>機種タイプ</t>
+          <t xml:space="preserve">機種タイプ</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>メディア区分</t>
+          <t xml:space="preserve">メディア区分</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ATタイプ</t>
+          <t xml:space="preserve">ATタイプ</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ボーナスタイプ</t>
+          <t xml:space="preserve">ボーナスタイプ</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>規則区分</t>
+          <t xml:space="preserve">規則区分</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>型式名</t>
+          <t xml:space="preserve">型式名</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>コイン単価</t>
+          <t xml:space="preserve">コイン単価</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>コイン単価条件</t>
+          <t xml:space="preserve">コイン単価条件</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>設定1出率</t>
+          <t xml:space="preserve">設定1出率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>設定2出率</t>
+          <t xml:space="preserve">設定2出率</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>設定3出率</t>
+          <t xml:space="preserve">設定3出率</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>設定4出率</t>
+          <t xml:space="preserve">設定4出率</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>設定5出率</t>
+          <t xml:space="preserve">設定5出率</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>設定6出率</t>
+          <t xml:space="preserve">設定6出率</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>出率条件</t>
+          <t xml:space="preserve">出率条件</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>出率出典URL</t>
+          <t xml:space="preserve">出率出典URL</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>コイン単価出典URL</t>
+          <t xml:space="preserve">コイン単価出典URL</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>メーカー出典URL</t>
+          <t xml:space="preserve">メーカー出典URL</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>データ取得日</t>
+          <t xml:space="preserve">データ取得日</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>現行判定</t>
+          <t xml:space="preserve">現行判定</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>信頼度</t>
+          <t xml:space="preserve">信頼度</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t xml:space="preserve">備考</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>別表記</t>
+          <t xml:space="preserve">別表記</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>マイジャグラーV</t>
+          <t xml:space="preserve">マイジャグラーV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>北電子</t>
+          <t xml:space="preserve">北電子</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aタイプ</t>
+          <t xml:space="preserve">Aタイプ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>メダル機</t>
+          <t xml:space="preserve">メダル機</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t xml:space="preserve">なし</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BIG／REG</t>
+          <t xml:space="preserve">BIG／REG</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6号機</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>97</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
+          <t xml:space="preserve">6号機</t>
+        </is>
+      </c>
+      <c r="K2">
+        <v>97.0</v>
+      </c>
+      <c r="P2">
         <v>109.4</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>不明（条件表記未確認）</t>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>https://nana-press.com/post/1546517 | https://slobase.jp/machines/myjuggler5</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
+          <t xml:space="preserve">https://nana-press.com/post/1546517 | https://slobase.jp/machines/myjuggler5</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.p-world.co.jp/machine/database/9514</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9514</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>現行</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t xml:space="preserve">低</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>設定2〜5未取得（検索結果に一覧表なし）。コイン単価未確認。ページ未検証。</t>
+          <t xml:space="preserve">設定2〜5未取得（検索結果に一覧表なし）。コイン単価未確認。ページ未検証。</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Sマイジャグラー5 / マイジャグ5 / マイジャグラー5</t>
+          <t xml:space="preserve">Sマイジャグラー5 / マイジャグ5 / マイジャグラー5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>スマスロ北斗の拳</t>
+          <t xml:space="preserve">スマスロ北斗の拳</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>サミー</t>
+          <t xml:space="preserve">サミー</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t xml:space="preserve">AT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>スマスロ</t>
+          <t xml:space="preserve">スマスロ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>バトルタイプAT（バトルボーナス）</t>
+          <t xml:space="preserve">バトルタイプAT（バトルボーナス）</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>疑似ボーナス</t>
+          <t xml:space="preserve">疑似ボーナス</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6.5号機</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="n">
+          <t xml:space="preserve">6.5号機</t>
+        </is>
+      </c>
+      <c r="I3">
         <v>3.3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>「約3.3円」との記載。算出条件（設定・回転数前提）不明</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>98</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>113</v>
+          <t xml:space="preserve">「約3.3円」との記載。算出条件（設定・回転数前提）不明</t>
+        </is>
+      </c>
+      <c r="K3">
+        <v>98.0</v>
+      </c>
+      <c r="P3">
+        <v>113.0</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>不明（条件表記未確認）</t>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>https://p-town.dmm.com/machines/4301 | https://p.hisshobon.jp/vpage.php?c=2517&amp;p=2</t>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/4301 | https://p.hisshobon.jp/vpage.php?c=2517&amp;p=2</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://altema.jp/pachimo/cointanka | https://homeslotnavi.xsrv.jp/sumasurokointankarankingu/</t>
+          <t xml:space="preserve">https://altema.jp/pachimo/cointanka | https://homeslotnavi.xsrv.jp/sumasurokointankarankingu/</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://chonborista.com/slot/sammy-slot/181626/</t>
+          <t xml:space="preserve">https://chonborista.com/slot/sammy-slot/181626/</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>現行</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>低</t>
+          <t xml:space="preserve">低</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>設定2〜5未取得（範囲表記98.0〜113.0%のみ）。コイン単価の算出条件不明。ページ未検証。</t>
+          <t xml:space="preserve">設定2〜5未取得（範囲表記98.0〜113.0%のみ）。コイン単価の算出条件不明。ページ未検証。</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>L北斗の拳 / 北斗の拳(スマスロ)</t>
+          <t xml:space="preserve">L北斗の拳 / 北斗の拳(スマスロ)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L ゴジラ対エヴァンゲリオン</t>
+          <t xml:space="preserve">L ゴジラ対エヴァンゲリオン</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ビスティ</t>
+          <t xml:space="preserve">ビスティ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t xml:space="preserve">AT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>スマスロ</t>
+          <t xml:space="preserve">スマスロ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ゴジエヴァRUSH</t>
+          <t xml:space="preserve">ゴジエヴァRUSH</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>疑似ボーナス</t>
+          <t xml:space="preserve">疑似ボーナス</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.5号機</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
+          <t xml:space="preserve">6.5号機</t>
+        </is>
+      </c>
+      <c r="K4">
         <v>97.7</v>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
+      <c r="P4">
         <v>114.9</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>不明（条件表記未確認）</t>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>https://www.p-world.co.jp/machine/database/9990 | https://p-town.dmm.com/machines/4501</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9990 | https://p-town.dmm.com/machines/4501</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://cs62.cs-plaza.com/g/pachi/pla/s_conq/bisty_slot/43/bisty_slot_43.php</t>
+          <t xml:space="preserve">https://cs62.cs-plaza.com/g/pachi/pla/s_conq/bisty_slot/43/bisty_slot_43.php</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>現行</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>低</t>
+          <t xml:space="preserve">低</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>設定2〜5未取得（範囲表記97.7〜114.9%のみ）。コイン単価未確認。ページ未検証。</t>
+          <t xml:space="preserve">設定2〜5未取得（範囲表記97.7〜114.9%のみ）。コイン単価未確認。ページ未検証。</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>スマスロ ゴジエヴァ / ゴジラvsエヴァンゲリオン</t>
+          <t xml:space="preserve">スマスロ ゴジエヴァ / ゴジラvsエヴァンゲリオン</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>スマスロ モンキーターンV</t>
+          <t xml:space="preserve">スマスロ モンキーターンV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>山佐</t>
+          <t xml:space="preserve">山佐</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t xml:space="preserve">AT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>スマスロ</t>
+          <t xml:space="preserve">スマスロ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AT（激走チャージ）</t>
+          <t xml:space="preserve">AT（激走チャージ）</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>疑似ボーナス</t>
+          <t xml:space="preserve">疑似ボーナス</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.5号機</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
+          <t xml:space="preserve">6.5号機</t>
+        </is>
+      </c>
+      <c r="K5">
+        <v>97.9</v>
+      </c>
+      <c r="N5">
         <v>104.5</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
+      <c r="P5">
         <v>114.9</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>不明（条件表記未確認）</t>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>https://www.p-world.co.jp/machine/database/9923 | https://hazuse.com/machine/pachislot/3S0772/</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9923 | https://hazuse.com/machine/pachislot/3S0772/</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://chonborista.com/slot/yamasa-slot/198173/</t>
+          <t xml:space="preserve">https://chonborista.com/slot/yamasa-slot/198173/</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>現行</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t xml:space="preserve">要確認</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>設定4=104.5%は検索結果要約の単独記述で一次ページ未確認のため要確認。設定2/3/5未取得。コイン単価未確認。ページ未検証。</t>
+          <t xml:space="preserve">設定4=104.5%は検索結果要約の単独記述で一次ページ未確認のため要確認。設定2/3/5未取得。コイン単価未確認。ページ未検証。</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>スマスロモンキーターンV / モンキーターン5</t>
+          <t xml:space="preserve">スマスロモンキーターンV / モンキーターン5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>押忍!番長ZERO</t>
+          <t xml:space="preserve">押忍!番長ZERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>大都技研</t>
+          <t xml:space="preserve">大都技研</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t xml:space="preserve">AT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>メダル機</t>
+          <t xml:space="preserve">メダル機</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AT（頂ロード）</t>
+          <t xml:space="preserve">AT（頂ロード）</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>疑似ボーナス</t>
+          <t xml:space="preserve">疑似ボーナス</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.2号機</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+          <t xml:space="preserve">6.2号機</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.p-world.co.jp/machine/database/9539</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9539</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>現行判定要確認</t>
+          <t xml:space="preserve">現行判定要確認</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t xml:space="preserve">要確認</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>出率を1つも取得できず（検索結果に数値記載なし）。コイン単価未確認。2022年導入の6.2号機のため現行判定要確認。ページ未検証。</t>
+          <t xml:space="preserve">出率を1つも取得できず（検索結果に数値記載なし）。コイン単価未確認。2022年導入の6.2号機のため現行判定要確認。ページ未検証。</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>L押忍!番長ZERO / 番長ゼロ / 番長0</t>
+          <t xml:space="preserve">L押忍!番長ZERO / 番長ゼロ / 番長0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>スマスロ からくりサーカス</t>
+          <t xml:space="preserve">スマスロ からくりサーカス</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>サミー</t>
+          <t xml:space="preserve">サミー</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t xml:space="preserve">AT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>スマスロ</t>
+          <t xml:space="preserve">スマスロ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AT（差枚数管理）</t>
+          <t xml:space="preserve">AT（差枚数管理）</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>疑似ボーナス</t>
+          <t xml:space="preserve">疑似ボーナス</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.5号機</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
+          <t xml:space="preserve">6.5号機</t>
+        </is>
+      </c>
+      <c r="K7">
         <v>97.5</v>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
+      <c r="O7">
         <v>108.1</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7">
         <v>114.9</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>不明（条件表記未確認）</t>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>https://www.p-world.co.jp/machine/database/9843 | https://altema.jp/pachimo/lkarakuri</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9843 | https://altema.jp/pachimo/lkarakuri</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://p-town.dmm.com/machines/4360</t>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/4360</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>現行</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t xml:space="preserve">要確認</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>設定5=108.1%は検索結果要約の単独記述で一次ページ未確認のため要確認。設定2/3/4未取得。コイン単価未確認。ページ未検証。</t>
+          <t xml:space="preserve">設定5=108.1%は検索結果要約の単独記述で一次ページ未確認のため要確認。設定2/3/4未取得。コイン単価未確認。ページ未検証。</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>パチスロ からくりサーカス / Lからくりサーカス</t>
+          <t xml:space="preserve">パチスロ からくりサーカス / Lからくりサーカス</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ゴーゴージャグラー3</t>
+          <t xml:space="preserve">ゴーゴージャグラー3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>北電子</t>
+          <t xml:space="preserve">北電子</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aタイプ</t>
+          <t xml:space="preserve">Aタイプ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>メダル機</t>
+          <t xml:space="preserve">メダル機</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t xml:space="preserve">なし</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BIG／REG</t>
+          <t xml:space="preserve">BIG／REG</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6号機</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
+          <t xml:space="preserve">6号機</t>
+        </is>
+      </c>
+      <c r="K8">
         <v>97.2</v>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
+      <c r="P8">
         <v>106.5</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>不明（条件表記未確認）</t>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>https://www.p-world.co.jp/machine/database/9848 | https://jugglersnet.com/analysis/gogo-juggler3</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9848 | https://jugglersnet.com/analysis/gogo-juggler3</t>
+        </is>
+      </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://p-town.dmm.com/machines/4375</t>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/4375</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>現行</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>低</t>
+          <t xml:space="preserve">低</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>設定2〜5未取得（範囲表記97.2〜106.5%のみ）。コイン単価未確認。ページ未検証。</t>
+          <t xml:space="preserve">設定2〜5未取得（範囲表記97.2〜106.5%のみ）。コイン単価未確認。ページ未検証。</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>ゴージャグ3 / Sゴーゴージャグラー3</t>
+          <t xml:space="preserve">ゴージャグ3 / Sゴーゴージャグラー3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ニューハナハナゴールド-30</t>
+          <t xml:space="preserve">ニューハナハナゴールド-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>パイオニア</t>
+          <t xml:space="preserve">パイオニア</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aタイプ</t>
+          <t xml:space="preserve">Aタイプ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>メダル機</t>
+          <t xml:space="preserve">メダル機</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t xml:space="preserve">なし</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BIG／REG</t>
+          <t xml:space="preserve">BIG／REG</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6号機</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+          <t xml:space="preserve">6号機</t>
+        </is>
+      </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.p-world.co.jp/machine/database/9267</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9267</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>現行判定要確認</t>
+          <t xml:space="preserve">現行判定要確認</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t xml:space="preserve">要確認</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>出率を1つも取得できず（検索結果はボーナス確率のみ記載）。コイン単価未確認。2020年導入のため現行判定要確認。ページ未検証。</t>
+          <t xml:space="preserve">出率を1つも取得できず（検索結果はボーナス確率のみ記載）。コイン単価未確認。2020年導入のため現行判定要確認。ページ未検証。</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>ハナハナゴールド</t>
+          <t xml:space="preserve">ハナハナゴールド</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L革命機ヴァルヴレイヴ</t>
+          <t xml:space="preserve">L革命機ヴァルヴレイヴ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t xml:space="preserve">不明</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t xml:space="preserve">AT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>スマスロ</t>
+          <t xml:space="preserve">スマスロ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>革命RUSH（純増約7.2枚/G）</t>
+          <t xml:space="preserve">革命RUSH（純増約7.2枚/G）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>疑似ボーナス</t>
+          <t xml:space="preserve">疑似ボーナス</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.5号機</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="n">
+          <t xml:space="preserve">6.5号機</t>
+        </is>
+      </c>
+      <c r="I10">
         <v>4.5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>設定1時の値との記載。算出条件（回転数前提）不明</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+          <t xml:space="preserve">設定1時の値との記載。算出条件（回転数前提）不明</t>
+        </is>
+      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://altema.jp/pachimo/kakumeikivalvrave</t>
+          <t xml:space="preserve">https://altema.jp/pachimo/kakumeikivalvrave</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://www.p-world.co.jp/machine/database/9725</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9725</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>現行</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t xml:space="preserve">要確認</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>メーカー要確認（解析サイトURLパスはSANKYO系を示唆するが確定情報なし。推測で埋めない方針により「不明」を維持）。出率を1つも取得できず。ページ未検証。</t>
+          <t xml:space="preserve">メーカー要確認（解析サイトURLパスはSANKYO系を示唆するが確定情報なし。推測で埋めない方針により「不明」を維持）。出率を1つも取得できず。ページ未検証。</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>スマスロ ヴヴヴ / パチスロ 革命機ヴァルヴレイヴ</t>
+          <t xml:space="preserve">スマスロ ヴヴヴ / パチスロ 革命機ヴァルヴレイヴ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lとある魔術の禁書目録2</t>
+          <t xml:space="preserve">Lとある魔術の禁書目録2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>藤商事</t>
+          <t xml:space="preserve">藤商事</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t xml:space="preserve">AT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>スマスロ</t>
+          <t xml:space="preserve">スマスロ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AT（通常約4.0枚/G、上位約7.0枚/G）</t>
+          <t xml:space="preserve">AT（通常約4.0枚/G、上位約7.0枚/G）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>疑似ボーナス</t>
+          <t xml:space="preserve">疑似ボーナス</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>スマスロ</t>
+          <t xml:space="preserve">スマスロ</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Lとある魔術の禁書目録2FA</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="L11" t="n">
+          <t xml:space="preserve">Lとある魔術の禁書目録2FA</t>
+        </is>
+      </c>
+      <c r="K11">
+        <v>97.9</v>
+      </c>
+      <c r="L11">
         <v>98.7</v>
       </c>
-      <c r="M11" t="n">
-        <v>100</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="M11">
+        <v>100.0</v>
+      </c>
+      <c r="N11">
         <v>104.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11">
         <v>108.2</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11">
         <v>113.3</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>不明（条件表記未確認）</t>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>https://www.slopachi-quest.com/article/toaru-majutsu-no-kinsho-mokuroku-2-settei/ | https://p-town.dmm.com/machines/5053</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr"/>
+          <t xml:space="preserve">https://www.slopachi-quest.com/article/toaru-majutsu-no-kinsho-mokuroku-2-settei/ | https://p-town.dmm.com/machines/5053</t>
+        </is>
+      </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://p-town.dmm.com/machines/5053</t>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/5053</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>現行</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>中</t>
+          <t xml:space="preserve">中</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>設定1〜6の全値を取得できた唯一の機種。ただし実質単一情報源かつページ未検証のため「中」止まり。メーカー表記は「藤商事／JFJ」。2026年8月3日導入。コイン単価未確認。</t>
+          <t xml:space="preserve">設定1〜6の全値を取得できた唯一の機種。ただし実質単一情報源かつページ未検証のため「中」止まり。メーカー表記は「藤商事／JFJ」。2026年8月3日導入。コイン単価未確認。</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>スマスロ とある魔術の禁書目録2 / インデックス2</t>
+          <t xml:space="preserve">スマスロ とある魔術の禁書目録2 / インデックス2</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Y11"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ランキング</t>
+          <t xml:space="preserve">ランキング</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>順位</t>
+          <t xml:space="preserve">順位</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>機種名</t>
+          <t xml:space="preserve">機種名</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>メーカー</t>
+          <t xml:space="preserve">メーカー</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>値</t>
+          <t xml:space="preserve">値</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>設定1出率ランキング</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+          <t xml:space="preserve">設定1出率ランキング</t>
+        </is>
+      </c>
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>スマスロ北斗の拳</t>
+          <t xml:space="preserve">スマスロ北斗の拳</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>サミー</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>98</v>
+          <t xml:space="preserve">サミー</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>98.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>スマスロ モンキーターンV</t>
+          <t xml:space="preserve">スマスロ モンキーターンV</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>山佐</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>97.90000000000001</v>
+          <t xml:space="preserve">山佐</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>97.9</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lとある魔術の禁書目録2</t>
+          <t xml:space="preserve">Lとある魔術の禁書目録2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>藤商事</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>97.90000000000001</v>
+          <t xml:space="preserve">藤商事</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>97.9</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>L ゴジラ対エヴァンゲリオン</t>
+          <t xml:space="preserve">L ゴジラ対エヴァンゲリオン</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ビスティ</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+          <t xml:space="preserve">ビスティ</t>
+        </is>
+      </c>
+      <c r="E5">
         <v>97.7</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>スマスロ からくりサーカス</t>
+          <t xml:space="preserve">スマスロ からくりサーカス</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>サミー</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
+          <t xml:space="preserve">サミー</t>
+        </is>
+      </c>
+      <c r="E6">
         <v>97.5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ゴーゴージャグラー3</t>
+          <t xml:space="preserve">ゴーゴージャグラー3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>北電子</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
+          <t xml:space="preserve">北電子</t>
+        </is>
+      </c>
+      <c r="E7">
         <v>97.2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>7</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>マイジャグラーV</t>
+          <t xml:space="preserve">マイジャグラーV</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>北電子</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-    </row>
+          <t xml:space="preserve">北電子</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>97.0</v>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>設定4出率ランキング</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+          <t xml:space="preserve">設定4出率ランキング</t>
+        </is>
+      </c>
+      <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>スマスロ モンキーターンV</t>
+          <t xml:space="preserve">スマスロ モンキーターンV</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>山佐</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
+          <t xml:space="preserve">山佐</t>
+        </is>
+      </c>
+      <c r="E10">
         <v>104.5</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lとある魔術の禁書目録2</t>
+          <t xml:space="preserve">Lとある魔術の禁書目録2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>藤商事</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
+          <t xml:space="preserve">藤商事</t>
+        </is>
+      </c>
+      <c r="E11">
         <v>104.5</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>設定5出率ランキング</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+          <t xml:space="preserve">設定5出率ランキング</t>
+        </is>
+      </c>
+      <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lとある魔術の禁書目録2</t>
+          <t xml:space="preserve">Lとある魔術の禁書目録2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>藤商事</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
+          <t xml:space="preserve">藤商事</t>
+        </is>
+      </c>
+      <c r="E13">
         <v>108.2</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>スマスロ からくりサーカス</t>
+          <t xml:space="preserve">スマスロ からくりサーカス</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>サミー</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+          <t xml:space="preserve">サミー</t>
+        </is>
+      </c>
+      <c r="E14">
         <v>108.1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>設定6出率ランキング</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+          <t xml:space="preserve">設定6出率ランキング</t>
+        </is>
+      </c>
+      <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L ゴジラ対エヴァンゲリオン</t>
+          <t xml:space="preserve">L ゴジラ対エヴァンゲリオン</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ビスティ</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
+          <t xml:space="preserve">ビスティ</t>
+        </is>
+      </c>
+      <c r="E16">
         <v>114.9</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>スマスロ モンキーターンV</t>
+          <t xml:space="preserve">スマスロ モンキーターンV</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>山佐</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
+          <t xml:space="preserve">山佐</t>
+        </is>
+      </c>
+      <c r="E17">
         <v>114.9</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>スマスロ からくりサーカス</t>
+          <t xml:space="preserve">スマスロ からくりサーカス</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>サミー</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
+          <t xml:space="preserve">サミー</t>
+        </is>
+      </c>
+      <c r="E18">
         <v>114.9</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>4</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lとある魔術の禁書目録2</t>
+          <t xml:space="preserve">Lとある魔術の禁書目録2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>藤商事</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
+          <t xml:space="preserve">藤商事</t>
+        </is>
+      </c>
+      <c r="E19">
         <v>113.3</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>スマスロ北斗の拳</t>
+          <t xml:space="preserve">スマスロ北斗の拳</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>サミー</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>113</v>
+          <t xml:space="preserve">サミー</t>
+        </is>
+      </c>
+      <c r="E20">
+        <v>113.0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>6</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>マイジャグラーV</t>
+          <t xml:space="preserve">マイジャグラーV</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>北電子</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
+          <t xml:space="preserve">北電子</t>
+        </is>
+      </c>
+      <c r="E21">
         <v>109.4</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>7</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ゴーゴージャグラー3</t>
+          <t xml:space="preserve">ゴーゴージャグラー3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>北電子</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
+          <t xml:space="preserve">北電子</t>
+        </is>
+      </c>
+      <c r="E22">
         <v>106.5</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>設定1→設定6 出率差ランキング</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
+          <t xml:space="preserve">設定1→設定6 出率差ランキング</t>
+        </is>
+      </c>
+      <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>スマスロ からくりサーカス</t>
+          <t xml:space="preserve">スマスロ からくりサーカス</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>サミー</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>17.40000000000001</v>
+          <t xml:space="preserve">サミー</t>
+        </is>
+      </c>
+      <c r="E24">
+        <v>17.4</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>2</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>L ゴジラ対エヴァンゲリオン</t>
+          <t xml:space="preserve">L ゴジラ対エヴァンゲリオン</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ビスティ</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
+          <t xml:space="preserve">ビスティ</t>
+        </is>
+      </c>
+      <c r="E25">
         <v>17.2</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>3</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>スマスロ モンキーターンV</t>
+          <t xml:space="preserve">スマスロ モンキーターンV</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>山佐</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>17</v>
+          <t xml:space="preserve">山佐</t>
+        </is>
+      </c>
+      <c r="E26">
+        <v>17.0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>4</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lとある魔術の禁書目録2</t>
+          <t xml:space="preserve">Lとある魔術の禁書目録2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>藤商事</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>15.39999999999999</v>
+          <t xml:space="preserve">藤商事</t>
+        </is>
+      </c>
+      <c r="E27">
+        <v>15.4</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>スマスロ北斗の拳</t>
+          <t xml:space="preserve">スマスロ北斗の拳</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>サミー</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>15</v>
+          <t xml:space="preserve">サミー</t>
+        </is>
+      </c>
+      <c r="E28">
+        <v>15.0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>6</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>マイジャグラーV</t>
+          <t xml:space="preserve">マイジャグラーV</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>北電子</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>12.40000000000001</v>
+          <t xml:space="preserve">北電子</t>
+        </is>
+      </c>
+      <c r="E29">
+        <v>12.4</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>7</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ゴーゴージャグラー3</t>
+          <t xml:space="preserve">ゴーゴージャグラー3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>北電子</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>9.299999999999997</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-    </row>
+          <t xml:space="preserve">北電子</t>
+        </is>
+      </c>
+      <c r="E30">
+        <v>9.3</v>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>コイン単価ランキング</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
+          <t xml:space="preserve">コイン単価ランキング</t>
+        </is>
+      </c>
+      <c r="B32">
         <v>1</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>L革命機ヴァルヴレイヴ</t>
+          <t xml:space="preserve">L革命機ヴァルヴレイヴ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
+          <t xml:space="preserve">不明</t>
+        </is>
+      </c>
+      <c r="E32">
         <v>4.5</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>2</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>スマスロ北斗の拳</t>
+          <t xml:space="preserve">スマスロ北斗の拳</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>サミー</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
+          <t xml:space="preserve">サミー</t>
+        </is>
+      </c>
+      <c r="E33">
         <v>3.3</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-    </row>
+    <row r="34"/>
   </sheetData>
   <autoFilter ref="A1:E34"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="59" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="60" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>機種名</t>
+          <t xml:space="preserve">機種名</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>メーカー</t>
+          <t xml:space="preserve">メーカー</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>信頼度</t>
+          <t xml:space="preserve">信頼度</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>要確認項目数</t>
+          <t xml:space="preserve">要確認項目数</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>要確認内容</t>
+          <t xml:space="preserve">要確認内容</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>出率出典URL</t>
+          <t xml:space="preserve">出率出典URL</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>データ取得日</t>
+          <t xml:space="preserve">データ取得日</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>マイジャグラーV</t>
+          <t xml:space="preserve">マイジャグラーV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>北電子</t>
+          <t xml:space="preserve">北電子</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+          <t xml:space="preserve">低</t>
+        </is>
+      </c>
+      <c r="D2">
         <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ コイン単価未確認 ／ 出率条件が不明</t>
+          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ コイン単価未確認 ／ 出率条件が不明</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://nana-press.com/post/1546517 | https://slobase.jp/machines/myjuggler5</t>
+          <t xml:space="preserve">https://nana-press.com/post/1546517 | https://slobase.jp/machines/myjuggler5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L ゴジラ対エヴァンゲリオン</t>
+          <t xml:space="preserve">L ゴジラ対エヴァンゲリオン</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ビスティ</t>
+          <t xml:space="preserve">ビスティ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+          <t xml:space="preserve">低</t>
+        </is>
+      </c>
+      <c r="D3">
         <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ コイン単価未確認 ／ 出率条件が不明</t>
+          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ コイン単価未確認 ／ 出率条件が不明</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.p-world.co.jp/machine/database/9990 | https://p-town.dmm.com/machines/4501</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9990 | https://p-town.dmm.com/machines/4501</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ゴーゴージャグラー3</t>
+          <t xml:space="preserve">スマスロ モンキーターンV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>北電子</t>
+          <t xml:space="preserve">山佐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+          <t xml:space="preserve">要確認</t>
+        </is>
+      </c>
+      <c r="D4">
         <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ コイン単価未確認 ／ 出率条件が不明</t>
+          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定5出率 ／ コイン単価未確認 ／ 出率条件が不明</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.p-world.co.jp/machine/database/9848 | https://jugglersnet.com/analysis/gogo-juggler3</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9923 | https://hazuse.com/machine/pachislot/3S0772/</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>スマスロ モンキーターンV</t>
+          <t xml:space="preserve">押忍!番長ZERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>山佐</t>
+          <t xml:space="preserve">大都技研</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+          <t xml:space="preserve">要確認</t>
+        </is>
+      </c>
+      <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>出率欠損: 設定2出率, 設定3出率, 設定5出率 ／ コイン単価未確認 ／ 出率条件が不明</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://www.p-world.co.jp/machine/database/9923 | https://hazuse.com/machine/pachislot/3S0772/</t>
+          <t xml:space="preserve">設定1〜6の出率が1つも入っていない（データ欠損） ／ コイン単価未確認 ／ 現行機かどうか不明（現行判定要確認）</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>押忍!番長ZERO</t>
+          <t xml:space="preserve">スマスロ からくりサーカス</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>大都技研</t>
+          <t xml:space="preserve">サミー</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+          <t xml:space="preserve">要確認</t>
+        </is>
+      </c>
+      <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>設定1〜6の出率が1つも入っていない（データ欠損） ／ コイン単価未確認 ／ 現行機かどうか不明（現行判定要確認）</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定4出率 ／ コイン単価未確認 ／ 出率条件が不明</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9843 | https://altema.jp/pachimo/lkarakuri</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>スマスロ からくりサーカス</t>
+          <t xml:space="preserve">ゴーゴージャグラー3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>サミー</t>
+          <t xml:space="preserve">北電子</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+          <t xml:space="preserve">低</t>
+        </is>
+      </c>
+      <c r="D7">
         <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>出率欠損: 設定2出率, 設定3出率, 設定4出率 ／ コイン単価未確認 ／ 出率条件が不明</t>
+          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ コイン単価未確認 ／ 出率条件が不明</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.p-world.co.jp/machine/database/9843 | https://altema.jp/pachimo/lkarakuri</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9848 | https://jugglersnet.com/analysis/gogo-juggler3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ニューハナハナゴールド-30</t>
+          <t xml:space="preserve">ニューハナハナゴールド-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>パイオニア</t>
+          <t xml:space="preserve">パイオニア</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+          <t xml:space="preserve">要確認</t>
+        </is>
+      </c>
+      <c r="D8">
         <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>設定1〜6の出率が1つも入っていない（データ欠損） ／ コイン単価未確認 ／ 現行機かどうか不明（現行判定要確認）</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t xml:space="preserve">設定1〜6の出率が1つも入っていない（データ欠損） ／ コイン単価未確認 ／ 現行機かどうか不明（現行判定要確認）</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>スマスロ北斗の拳</t>
+          <t xml:space="preserve">スマスロ北斗の拳</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>サミー</t>
+          <t xml:space="preserve">サミー</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+          <t xml:space="preserve">低</t>
+        </is>
+      </c>
+      <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ 出率条件が不明</t>
+          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ 出率条件が不明</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://p-town.dmm.com/machines/4301 | https://p.hisshobon.jp/vpage.php?c=2517&amp;p=2</t>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/4301 | https://p.hisshobon.jp/vpage.php?c=2517&amp;p=2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L革命機ヴァルヴレイヴ</t>
+          <t xml:space="preserve">L革命機ヴァルヴレイヴ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t xml:space="preserve">不明</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+          <t xml:space="preserve">要確認</t>
+        </is>
+      </c>
+      <c r="D10">
         <v>2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>設定1〜6の出率が1つも入っていない（データ欠損） ／ メーカー不明</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t xml:space="preserve">設定1〜6の出率が1つも入っていない（データ欠損） ／ メーカー不明</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lとある魔術の禁書目録2</t>
+          <t xml:space="preserve">Lとある魔術の禁書目録2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>藤商事</t>
+          <t xml:space="preserve">藤商事</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+          <t xml:space="preserve">中</t>
+        </is>
+      </c>
+      <c r="D11">
         <v>2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>コイン単価未確認 ／ 出率条件が不明</t>
+          <t xml:space="preserve">コイン単価未確認 ／ 出率条件が不明</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.slopachi-quest.com/article/toaru-majutsu-no-kinsho-mokuroku-2-settei/ | https://p-town.dmm.com/machines/5053</t>
+          <t xml:space="preserve">https://www.slopachi-quest.com/article/toaru-majutsu-no-kinsho-mokuroku-2-settei/ | https://p-town.dmm.com/machines/5053</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G11"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="49" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="5" max="5" width="49" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>機種名</t>
+          <t xml:space="preserve">機種名</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>メーカー</t>
+          <t xml:space="preserve">メーカー</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>取得できなかった理由</t>
+          <t xml:space="preserve">取得できなかった理由</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>試した情報源</t>
+          <t xml:space="preserve">試した情報源</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t xml:space="preserve">URL</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>再調査が必要か</t>
+          <t xml:space="preserve">再調査が必要か</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>押忍!番長ZERO</t>
+          <t xml:space="preserve">押忍!番長ZERO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大都技研</t>
+          <t xml:space="preserve">大都技研</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>検索結果に機械割の数値記載がなく、一次ページ（ななプレス等）がegressブロックで開けない</t>
+          <t xml:space="preserve">検索結果に機械割の数値記載がなく、一次ページ（ななプレス等）がegressブロックで開けない</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P-WORLD / DMMぱちタウン / ななプレス / ちょんぼりすた</t>
+          <t xml:space="preserve">P-WORLD / DMMぱちタウン / ななプレス / ちょんぼりすた</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.p-world.co.jp/machine/database/9539</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9539</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>要</t>
+          <t xml:space="preserve">要</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ニューハナハナゴールド-30</t>
+          <t xml:space="preserve">ニューハナハナゴールド-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>パイオニア</t>
+          <t xml:space="preserve">パイオニア</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>検索結果に機械割の数値記載がなく、一次ページ（スロベース/P-WORLD）がegressブロックで開けない</t>
+          <t xml:space="preserve">検索結果に機械割の数値記載がなく、一次ページ（スロベース/P-WORLD）がegressブロックで開けない</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P-WORLD / DMMぱちタウン / スロベース / 一撃</t>
+          <t xml:space="preserve">P-WORLD / DMMぱちタウン / スロベース / 一撃</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.p-world.co.jp/machine/database/9267</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9267</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>要</t>
+          <t xml:space="preserve">要</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L革命機ヴァルヴレイヴ</t>
+          <t xml:space="preserve">L革命機ヴァルヴレイヴ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t xml:space="preserve">不明</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>検索結果に機械割の数値記載なし。メーカーも一次情報未確認</t>
+          <t xml:space="preserve">検索結果に機械割の数値記載なし。メーカーも一次情報未確認</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P-WORLD / アルテマ / 一撃 / ちょんぼりすた</t>
+          <t xml:space="preserve">P-WORLD / アルテマ / 一撃 / ちょんぼりすた</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.p-world.co.jp/machine/database/9725</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9725</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>要</t>
+          <t xml:space="preserve">要</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F4"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pachislot-db/output/slot_machine_database.xlsx
+++ b/pachislot-db/output/slot_machine_database.xlsx
@@ -67,19 +67,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="45" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="36" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="55" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
     <col min="12" max="12" width="11" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
@@ -88,13 +88,13 @@
     <col min="16" max="16" width="11" customWidth="1"/>
     <col min="17" max="17" width="24" customWidth="1"/>
     <col min="18" max="18" width="60" customWidth="1"/>
-    <col min="19" max="19" width="60" customWidth="1"/>
+    <col min="19" max="19" width="19" customWidth="1"/>
     <col min="20" max="20" width="60" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
     <col min="22" max="22" width="16" customWidth="1"/>
     <col min="23" max="23" width="10" customWidth="1"/>
     <col min="24" max="24" width="60" customWidth="1"/>
-    <col min="25" max="25" width="50" customWidth="1"/>
+    <col min="25" max="25" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -227,37 +227,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">マイジャグラーV</t>
+          <t xml:space="preserve">マイジャグラーVI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t xml:space="preserve">北電子</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aタイプ</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">メダル機</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">なし</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BIG／REG</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6号機</t>
         </is>
       </c>
       <c r="K2">
@@ -273,22 +248,22 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://nana-press.com/post/1546517 | https://slobase.jp/machines/myjuggler5</t>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/5054</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9514</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10513 | https://p-town.dmm.com/machines/5054</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t xml:space="preserve">現行</t>
+          <t xml:space="preserve">現行判定要確認</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -298,152 +273,68 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定2〜5未取得（検索結果に一覧表なし）。コイン単価未確認。ページ未検証。</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sマイジャグラー5 / マイジャグ5 / マイジャグラー5</t>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『北電子』/ DMMぱちタウン『北電子(メーカー公式サイト) 北電子』） ／ 設置店舗数の記載を確認できず、現行稼働かを判断できない ／ DMMぱちタウンの範囲表記からの設定1・6のみ。設定2〜5は範囲表記のため取得できず空欄 ／ 検定番号 5S0437 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">スマスロ北斗の拳</t>
+          <t xml:space="preserve">スマスロパリピ孔明</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サミー</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AT</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">スマスロ</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">バトルタイプAT（バトルボーナス）</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">疑似ボーナス</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.5号機</t>
-        </is>
-      </c>
-      <c r="I3">
-        <v>3.3</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「約3.3円」との記載。算出条件（設定・回転数前提）不明</t>
-        </is>
-      </c>
-      <c r="K3">
-        <v>98.0</v>
-      </c>
-      <c r="P3">
-        <v>113.0</v>
+          <t xml:space="preserve">山佐</t>
+        </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t xml:space="preserve">不明（条件表記未確認）</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://p-town.dmm.com/machines/4301 | https://p.hisshobon.jp/vpage.php?c=2517&amp;p=2</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://altema.jp/pachimo/cointanka | https://homeslotnavi.xsrv.jp/sumasurokointankarankingu/</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://chonborista.com/slot/sammy-slot/181626/</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10518 | https://p-town.dmm.com/machines/5057</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t xml:space="preserve">現行</t>
+          <t xml:space="preserve">現行判定要確認</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t xml:space="preserve">低</t>
+          <t xml:space="preserve">要確認</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定2〜5未取得（範囲表記98.0〜113.0%のみ）。コイン単価の算出条件不明。ページ未検証。</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L北斗の拳 / 北斗の拳(スマスロ)</t>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『山佐』/ DMMぱちタウン『山佐(メーカー公式サイト) 山佐』） ／ 設置店舗数の記載を確認できず、現行稼働かを判断できない ／ 検定番号 6S0292 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">L ゴジラ対エヴァンゲリオン</t>
+          <t xml:space="preserve">スマスロ 獣王</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビスティ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AT</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">スマスロ</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ゴジエヴァRUSH</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">疑似ボーナス</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.5号機</t>
+          <t xml:space="preserve">サミー</t>
         </is>
       </c>
       <c r="K4">
-        <v>97.7</v>
+        <v>97.8</v>
       </c>
       <c r="P4">
-        <v>114.9</v>
+        <v>114.3</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -452,22 +343,22 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9990 | https://p-town.dmm.com/machines/4501</t>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/5061</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://cs62.cs-plaza.com/g/pachi/pla/s_conq/bisty_slot/43/bisty_slot_43.php</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10521 | https://p-town.dmm.com/machines/5061</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t xml:space="preserve">現行</t>
+          <t xml:space="preserve">現行判定要確認</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -477,83 +368,39 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定2〜5未取得（範囲表記97.7〜114.9%のみ）。コイン単価未確認。ページ未検証。</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">スマスロ ゴジエヴァ / ゴジラvsエヴァンゲリオン</t>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『サミー』/ DMMぱちタウン『サミー(メーカー公式サイト) サミー』） ／ 設置店舗数の記載を確認できず、現行稼働かを判断できない ／ DMMぱちタウンの範囲表記からの設定1・6のみ。設定2〜5は範囲表記のため取得できず空欄 ／ 検定番号 6S0560 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">スマスロ モンキーターンV</t>
+          <t xml:space="preserve">L 転生王女と天才令嬢の魔法革命</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">山佐</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AT</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">スマスロ</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AT（激走チャージ）</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">疑似ボーナス</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.5号機</t>
-        </is>
-      </c>
-      <c r="K5">
-        <v>97.9</v>
-      </c>
-      <c r="N5">
-        <v>104.5</v>
-      </c>
-      <c r="P5">
-        <v>114.9</v>
+          <t xml:space="preserve">オリンピアエステート</t>
+        </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t xml:space="preserve">不明（条件表記未確認）</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9923 | https://hazuse.com/machine/pachislot/3S0772/</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://chonborista.com/slot/yamasa-slot/198173/</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10550 | https://p-town.dmm.com/machines/5086</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t xml:space="preserve">現行</t>
+          <t xml:space="preserve">現行判定要確認</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -563,59 +410,39 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定4=104.5%は検索結果要約の単独記述で一次ページ未確認のため要確認。設定2/3/5未取得。コイン単価未確認。ページ未検証。</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">スマスロモンキーターンV / モンキーターン5</t>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『オリンピアエステート』/ DMMぱちタウン『オリンピアエステート(メーカー公式サイト) オリンピアエステート』） ／ 設置店舗数の記載を確認できず、現行稼働かを判断できない ／ 検定番号 6S0429 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">押忍!番長ZERO</t>
+          <t xml:space="preserve">モグモグ風林火山 大海戦の巻</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">大都技研</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AT</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">メダル機</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AT（頂ロード）</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">疑似ボーナス</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.2号機</t>
+          <t xml:space="preserve">ネット</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lモグモグ風林火山 大海戦の巻ZB</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9539</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10523 | https://p-town.dmm.com/machines/5059</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -630,56 +457,28 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t xml:space="preserve">出率を1つも取得できず（検索結果に数値記載なし）。コイン単価未確認。2022年導入の6.2号機のため現行判定要確認。ページ未検証。</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L押忍!番長ZERO / 番長ゼロ / 番長0</t>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『ネット』/ DMMぱちタウン『ネット(メーカー公式サイト) ネット』） ／ 設置店舗数の記載を確認できず、現行稼働かを判断できない ／ 検定番号 531225 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">スマスロ からくりサーカス</t>
+          <t xml:space="preserve">パチスロ見える子ちゃん</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">サミー</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AT</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">スマスロ</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AT（差枚数管理）</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">疑似ボーナス</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.5号機</t>
+          <t xml:space="preserve">パイオニア</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L見える子ちゃんSC</t>
         </is>
       </c>
       <c r="K7">
-        <v>97.5</v>
-      </c>
-      <c r="O7">
-        <v>108.1</v>
+        <v>97.8</v>
       </c>
       <c r="P7">
         <v>114.9</v>
@@ -691,81 +490,68 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9843 | https://altema.jp/pachimo/lkarakuri</t>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/5042</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://p-town.dmm.com/machines/4360</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10501 | https://p-town.dmm.com/machines/5042</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t xml:space="preserve">現行</t>
+          <t xml:space="preserve">現行判定要確認</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t xml:space="preserve">要確認</t>
+          <t xml:space="preserve">低</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定5=108.1%は検索結果要約の単独記述で一次ページ未確認のため要確認。設定2/3/4未取得。コイン単価未確認。ページ未検証。</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">パチスロ からくりサーカス / Lからくりサーカス</t>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『パイオニア』/ DMMぱちタウン『パイオニア(メーカー公式サイト) パイオニア』） ／ 設置店舗数の記載を確認できず、現行稼働かを判断できない ／ DMMぱちタウンの範囲表記からの設定1・6のみ。設定2〜5は範囲表記のため取得できず空欄 ／ 検定番号 6S0265 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ゴーゴージャグラー3</t>
+          <t xml:space="preserve">スマスロ リコリス・リコイル</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">北電子</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aタイプ</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">メダル機</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">なし</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BIG／REG</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6号機</t>
+          <t xml:space="preserve">サミー</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L スマスロ リコリス・リコイル KX</t>
         </is>
       </c>
       <c r="K8">
-        <v>97.2</v>
+        <v>97.9</v>
+      </c>
+      <c r="L8">
+        <v>98.9</v>
+      </c>
+      <c r="M8">
+        <v>101.3</v>
+      </c>
+      <c r="N8">
+        <v>106.1</v>
+      </c>
+      <c r="O8">
+        <v>110.4</v>
       </c>
       <c r="P8">
-        <v>106.5</v>
+        <v>114.6</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -774,84 +560,75 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9848 | https://jugglersnet.com/analysis/gogo-juggler3</t>
+          <t xml:space="preserve">https://slobase.jp/machines/lycoris-recoil | https://p-town.dmm.com/machines/5033</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://p-town.dmm.com/machines/4375</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10503 | https://p-town.dmm.com/machines/5033</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">現行</t>
+          <t xml:space="preserve">現行判定要確認</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t xml:space="preserve">低</t>
+          <t xml:space="preserve">高</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定2〜5未取得（範囲表記97.2〜106.5%のみ）。コイン単価未確認。ページ未検証。</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ゴージャグ3 / Sゴーゴージャグラー3</t>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『サミー』/ DMMぱちタウン『サミー(メーカー公式サイト) サミー』） ／ 設置店舗数の記載を確認できず、現行稼働かを判断できない ／ 設定1・6の出率が2情報源で一致 ／ 検定番号 6S0400 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ニューハナハナゴールド-30</t>
+          <t xml:space="preserve">スマスロ タコスロ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">パイオニア</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aタイプ</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">メダル機</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">なし</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BIG／REG</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6号機</t>
+          <t xml:space="preserve">ユニバーサルブロス</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LB/タコスロBD</t>
+        </is>
+      </c>
+      <c r="K9">
+        <v>98.7</v>
+      </c>
+      <c r="P9">
+        <v>108.5</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/5049</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9267</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10510 | https://p-town.dmm.com/machines/5049</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -861,214 +638,810 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t xml:space="preserve">要確認</t>
+          <t xml:space="preserve">低</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t xml:space="preserve">出率を1つも取得できず（検索結果はボーナス確率のみ記載）。コイン単価未確認。2020年導入のため現行判定要確認。ページ未検証。</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ハナハナゴールド</t>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『ユニバーサルブロス』/ DMMぱちタウン『ユニバーサルブロス(メーカー公式サイト) ユニバーサルブロス』） ／ 設置店舗数の記載を確認できず、現行稼働かを判断できない ／ DMMぱちタウンの範囲表記からの設定1・6のみ。設定2〜5は範囲表記のため取得できず空欄 ／ 検定番号 6S0085 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">L革命機ヴァルヴレイヴ</t>
+          <t xml:space="preserve">L青春ブタ野郎はバニーガール先輩の夢を見ない</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">不明</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AT</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">スマスロ</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">革命RUSH（純増約7.2枚/G）</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">疑似ボーナス</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.5号機</t>
-        </is>
-      </c>
-      <c r="I10">
-        <v>4.5</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">設定1時の値との記載。算出条件（回転数前提）不明</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://altema.jp/pachimo/kakumeikivalvrave</t>
+          <t xml:space="preserve">オリンピア</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L青春ブタ野郎L1</t>
+        </is>
+      </c>
+      <c r="K10">
+        <v>98.1</v>
+      </c>
+      <c r="P10">
+        <v>110.3</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/5064</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9725</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10527 | https://p-town.dmm.com/machines/5064</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t xml:space="preserve">現行</t>
+          <t xml:space="preserve">現行判定要確認</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t xml:space="preserve">要確認</t>
+          <t xml:space="preserve">低</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t xml:space="preserve">メーカー要確認（解析サイトURLパスはSANKYO系を示唆するが確定情報なし。推測で埋めない方針により「不明」を維持）。出率を1つも取得できず。ページ未検証。</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">スマスロ ヴヴヴ / パチスロ 革命機ヴァルヴレイヴ</t>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『オリンピア』/ DMMぱちタウン『オリンピア(メーカー公式サイト) オリンピア』） ／ 設置店舗数の記載を確認できず、現行稼働かを判断できない ／ DMMぱちタウンの範囲表記からの設定1・6のみ。設定2〜5は範囲表記のため取得できず空欄 ／ 検定番号 630379 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lとある魔術の禁書目録2</t>
+          <t xml:space="preserve">Lパチスロ 彼女、お借りします</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t xml:space="preserve">SANKYO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lレンタル彼女bK</t>
+        </is>
+      </c>
+      <c r="K11">
+        <v>97.7</v>
+      </c>
+      <c r="P11">
+        <v>114.9</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/5065</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10543 | https://p-town.dmm.com/machines/5065</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行判定要確認</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">低</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『SANKYO』/ DMMぱちタウン『SANKYO(メーカー公式サイト) SANKYO』） ／ 設置店舗数の記載を確認できず、現行稼働かを判断できない ／ DMMぱちタウンの範囲表記からの設定1・6のみ。設定2〜5は範囲表記のため取得できず空欄 ／ 検定番号 630270 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lパチスロ 喰霊-零-Re</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">オーイズミ</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lパチスロ喰霊零Re/L3</t>
+        </is>
+      </c>
+      <c r="K12">
+        <v>97.8</v>
+      </c>
+      <c r="L12">
+        <v>98.9</v>
+      </c>
+      <c r="M12">
+        <v>101.0</v>
+      </c>
+      <c r="N12">
+        <v>104.4</v>
+      </c>
+      <c r="O12">
+        <v>106.9</v>
+      </c>
+      <c r="P12">
+        <v>110.0</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://slobase.jp/machines/garei-zero-re | https://p-town.dmm.com/machines/5028</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10530 | https://p-town.dmm.com/machines/5028</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行判定要確認</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『オーイズミ』/ DMMぱちタウン『オーイズミ(メーカー公式サイト) オーイズミ』） ／ 設置店舗数の記載を確認できず、現行稼働かを判断できない ／ 設定1・6の出率が2情報源で一致 ／ 検定番号 530560 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スロット ワールドダイスター</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">パオン・ディーピー</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L/ワールドダイスター/PA3</t>
+        </is>
+      </c>
+      <c r="K13">
+        <v>97.8</v>
+      </c>
+      <c r="P13">
+        <v>112.4</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/5055</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10517 | https://p-town.dmm.com/machines/5055</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行判定要確認</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">低</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『パオン・ディーピー』/ DMMぱちタウン『パオン・ディーピー(メーカー公式サイト) パオン・ディーピー』） ／ 設置店舗数 2,997店舗（P-WORLD調べ 調査日2026-02-04） ／ DMMぱちタウンの範囲表記からの設定1・6のみ。設定2〜5は範囲表記のため取得できず空欄 ／ 検定番号 6S0003 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ ストリートファイター6</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">レオスター</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lストリートファイター6SB</t>
+        </is>
+      </c>
+      <c r="K14">
+        <v>97.4</v>
+      </c>
+      <c r="L14">
+        <v>98.4</v>
+      </c>
+      <c r="M14">
+        <v>100.4</v>
+      </c>
+      <c r="N14">
+        <v>103.2</v>
+      </c>
+      <c r="O14">
+        <v>106.1</v>
+      </c>
+      <c r="P14">
+        <v>110.0</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://slobase.jp/machines/street-fighter6 | https://p-town.dmm.com/machines/5068</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10531 | https://p-town.dmm.com/machines/5068</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行判定要確認</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『レオスター』/ DMMぱちタウン『レオスター(メーカー公式サイト) レオスター』） ／ 設置店舗数 3,659店舗（P-WORLD調べ 調査日2026-02-04） ／ 設定1・6の出率が2情報源で一致 ／ 検定番号 6S0125 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ とんでもスキルで異世界放浪メシ</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コナミアミューズメント</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LとんでもスキルKM</t>
+        </is>
+      </c>
+      <c r="K15">
+        <v>97.9</v>
+      </c>
+      <c r="L15">
+        <v>99.1</v>
+      </c>
+      <c r="M15">
+        <v>101.0</v>
+      </c>
+      <c r="N15">
+        <v>105.3</v>
+      </c>
+      <c r="O15">
+        <v>109.1</v>
+      </c>
+      <c r="P15">
+        <v>112.1</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://slobase.jp/machines/tondemo-skill | https://p-town.dmm.com/machines/5030</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10493 | https://p-town.dmm.com/machines/5030</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行判定要確認</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『コナミアミューズメント』/ DMMぱちタウン『コナミアミューズメント(メーカー公式サイト) コナミアミューズメント』） ／ 設置店舗数 1,372店舗（P-WORLD調べ 調査日2026-02-04） ／ 設定1・6の出率が2情報源で一致 ／ 検定番号 5S1909 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ とある魔術の禁書目録2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t xml:space="preserve">藤商事</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AT</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">スマスロ</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AT（通常約4.0枚/G、上位約7.0枚/G）</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">疑似ボーナス</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">スマスロ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve">Lとある魔術の禁書目録2FA</t>
         </is>
       </c>
-      <c r="K11">
+      <c r="K16">
         <v>97.9</v>
       </c>
-      <c r="L11">
+      <c r="L16">
         <v>98.7</v>
       </c>
-      <c r="M11">
+      <c r="M16">
         <v>100.0</v>
       </c>
-      <c r="N11">
+      <c r="N16">
         <v>104.5</v>
       </c>
-      <c r="O11">
+      <c r="O16">
         <v>108.2</v>
       </c>
-      <c r="P11">
+      <c r="P16">
         <v>113.3</v>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t xml:space="preserve">不明（条件表記未確認）</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.slopachi-quest.com/article/toaru-majutsu-no-kinsho-mokuroku-2-settei/ | https://p-town.dmm.com/machines/5053</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://p-town.dmm.com/machines/5053</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-12</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">現行</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">設定1〜6の全値を取得できた唯一の機種。ただし実質単一情報源かつページ未検証のため「中」止まり。メーカー表記は「藤商事／JFJ」。2026年8月3日導入。コイン単価未確認。</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">スマスロ とある魔術の禁書目録2 / インデックス2</t>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://slobase.jp/machines/toaru-majutsu2 | https://p-town.dmm.com/machines/5053</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10516 | https://p-town.dmm.com/machines/5053</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行判定要確認</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『藤商事』/ DMMぱちタウン『藤商事(メーカー公式サイト) 藤商事』） ／ 設置店舗数 3,506店舗（P-WORLD調べ 調査日2026-02-04） ／ 設定1・6の出率が2情報源で一致 ／ 検定番号 5S1883 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L邪神ちゃんドロップキック</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サンスリー</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L邪神ちゃんドロップキックTX</t>
+        </is>
+      </c>
+      <c r="K17">
+        <v>97.8</v>
+      </c>
+      <c r="L17">
+        <v>98.6</v>
+      </c>
+      <c r="M17">
+        <v>100.4</v>
+      </c>
+      <c r="N17">
+        <v>106.1</v>
+      </c>
+      <c r="O17">
+        <v>110.4</v>
+      </c>
+      <c r="P17">
+        <v>114.1</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://slobase.jp/machines/jashin-chan-dropkick | https://p-town.dmm.com/machines/5020</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10498 | https://p-town.dmm.com/machines/5020</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行判定要確認</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『サンスリー』/ DMMぱちタウン『三洋(メーカー公式サイト) 三洋』） ／ 設置店舗数 2,790店舗（P-WORLD調べ 調査日2026-02-04） ／ 設定1・6の出率が2情報源で一致 ／ 検定番号 5S1821 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lすーぱぁびん娘</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベルコ</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lびん娘NY1</t>
+        </is>
+      </c>
+      <c r="K18">
+        <v>97.3</v>
+      </c>
+      <c r="L18">
+        <v>98.9</v>
+      </c>
+      <c r="N18">
+        <v>103.3</v>
+      </c>
+      <c r="O18">
+        <v>107.2</v>
+      </c>
+      <c r="P18">
+        <v>112.5</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://slobase.jp/machines/super-bin-musume | https://p-town.dmm.com/machines/5038</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10496 | https://p-town.dmm.com/machines/5038</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行判定要確認</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『ベルコ』/ DMMぱちタウン『ベルコ(メーカー公式サイト) ベルコ』） ／ 設置店舗数 213店舗（P-WORLD調べ 調査日2026-02-04） ／ 設定1・6の出率が2情報源で一致 ／ 検定番号 5S1500 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LBトリプルクラウンX-300</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">清龍ゲームジャパン</t>
+        </is>
+      </c>
+      <c r="K19">
+        <v>97.0</v>
+      </c>
+      <c r="P19">
+        <v>110.0</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/5089</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10542 | https://p-town.dmm.com/machines/5089</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行判定要確認</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">低</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『清龍ゲームジャパン』/ DMMぱちタウン『清龍ジャパン(メーカー公式サイト) 清龍ジャパン』） ／ 設置店舗数 6店舗（P-WORLD調べ 調査日2026-02-04） ／ DMMぱちタウンの範囲表記からの設定1・6のみ。設定2〜5は範囲表記のため取得できず空欄 ／ 検定番号 531140 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">戦国コレクション6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コナミアミューズメント</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L戦国コレクション6KS</t>
+        </is>
+      </c>
+      <c r="K20">
+        <v>97.9</v>
+      </c>
+      <c r="L20">
+        <v>99.1</v>
+      </c>
+      <c r="M20">
+        <v>100.9</v>
+      </c>
+      <c r="N20">
+        <v>106.0</v>
+      </c>
+      <c r="O20">
+        <v>110.1</v>
+      </c>
+      <c r="P20">
+        <v>114.9</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://slobase.jp/machines/sengoku-collection6 | https://p-town.dmm.com/machines/5010</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10471 | https://p-town.dmm.com/machines/5010</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行判定要確認</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『コナミアミューズメント』/ DMMぱちタウン『コナミアミューズメント(メーカー公式サイト) コナミアミューズメント』） ／ 設置店舗数 3,867店舗（P-WORLD調べ 調査日2026-02-04） ／ 設定1・6の出率が2情報源で一致 ／ 検定番号 5S1589 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ローティス</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">北電子</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LローティスTN</t>
+        </is>
+      </c>
+      <c r="K21">
+        <v>98.0</v>
+      </c>
+      <c r="L21">
+        <v>99.6</v>
+      </c>
+      <c r="N21">
+        <v>102.7</v>
+      </c>
+      <c r="O21">
+        <v>105.0</v>
+      </c>
+      <c r="P21">
+        <v>108.1</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不明（条件表記未確認）</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://slobase.jp/machines/rotis | https://p-town.dmm.com/machines/5029</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10491 | https://p-town.dmm.com/machines/5029</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行判定要確認</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">メーカー表記が情報源間で不一致（P-WORLD『北電子』/ DMMぱちタウン『北電子(メーカー公式サイト) 北電子』） ／ 設置店舗数 1,576店舗（P-WORLD調べ 調査日2026-02-04） ／ 設定1・6の出率が2情報源で一致 ／ 検定番号 531154 ／ コイン単価未確認 ／ 規則区分をP-WORLDのタイプ欄で確認できず、対象範囲か判断できない</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y11"/>
+  <autoFilter ref="A1:Y21"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1110,16 +1483,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">スマスロ北斗の拳</t>
+          <t xml:space="preserve">スマスロ タコスロ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">サミー</t>
+          <t xml:space="preserve">ユニバーサルブロス</t>
         </is>
       </c>
       <c r="E2">
-        <v>98.0</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="3">
@@ -1128,16 +1501,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">スマスロ モンキーターンV</t>
+          <t xml:space="preserve">L青春ブタ野郎はバニーガール先輩の夢を見ない</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">山佐</t>
+          <t xml:space="preserve">オリンピア</t>
         </is>
       </c>
       <c r="E3">
-        <v>97.9</v>
+        <v>98.1</v>
       </c>
     </row>
     <row r="4">
@@ -1146,16 +1519,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lとある魔術の禁書目録2</t>
+          <t xml:space="preserve">ローティス</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">藤商事</t>
+          <t xml:space="preserve">北電子</t>
         </is>
       </c>
       <c r="E4">
-        <v>97.9</v>
+        <v>98.0</v>
       </c>
     </row>
     <row r="5">
@@ -1164,16 +1537,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">L ゴジラ対エヴァンゲリオン</t>
+          <t xml:space="preserve">スマスロ リコリス・リコイル</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビスティ</t>
+          <t xml:space="preserve">サミー</t>
         </is>
       </c>
       <c r="E5">
-        <v>97.7</v>
+        <v>97.9</v>
       </c>
     </row>
     <row r="6">
@@ -1182,16 +1555,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">スマスロ からくりサーカス</t>
+          <t xml:space="preserve">スマスロ とんでもスキルで異世界放浪メシ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">サミー</t>
+          <t xml:space="preserve">コナミアミューズメント</t>
         </is>
       </c>
       <c r="E6">
-        <v>97.5</v>
+        <v>97.9</v>
       </c>
     </row>
     <row r="7">
@@ -1200,16 +1573,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ゴーゴージャグラー3</t>
+          <t xml:space="preserve">スマスロ とある魔術の禁書目録2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">北電子</t>
+          <t xml:space="preserve">藤商事</t>
         </is>
       </c>
       <c r="E7">
-        <v>97.2</v>
+        <v>97.9</v>
       </c>
     </row>
     <row r="8">
@@ -1218,421 +1591,1183 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">マイジャグラーV</t>
+          <t xml:space="preserve">戦国コレクション6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">北電子</t>
+          <t xml:space="preserve">コナミアミューズメント</t>
         </is>
       </c>
       <c r="E8">
-        <v>97.0</v>
-      </c>
-    </row>
-    <row r="9"/>
+        <v>97.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ 獣王</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サミー</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>97.8</v>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">設定4出率ランキング</t>
-        </is>
-      </c>
       <c r="B10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">スマスロ モンキーターンV</t>
+          <t xml:space="preserve">パチスロ見える子ちゃん</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">山佐</t>
+          <t xml:space="preserve">パイオニア</t>
         </is>
       </c>
       <c r="E10">
-        <v>104.5</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="11">
       <c r="B11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lとある魔術の禁書目録2</t>
+          <t xml:space="preserve">Lパチスロ 喰霊-零-Re</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">藤商事</t>
+          <t xml:space="preserve">オーイズミ</t>
         </is>
       </c>
       <c r="E11">
-        <v>104.5</v>
-      </c>
-    </row>
-    <row r="12"/>
+        <v>97.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スロット ワールドダイスター</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">パオン・ディーピー</t>
+        </is>
+      </c>
+      <c r="E12">
+        <v>97.8</v>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">設定5出率ランキング</t>
-        </is>
-      </c>
       <c r="B13">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lとある魔術の禁書目録2</t>
+          <t xml:space="preserve">L邪神ちゃんドロップキック</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">藤商事</t>
+          <t xml:space="preserve">サンスリー</t>
         </is>
       </c>
       <c r="E13">
-        <v>108.2</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="14">
       <c r="B14">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">スマスロ からくりサーカス</t>
+          <t xml:space="preserve">Lパチスロ 彼女、お借りします</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">サミー</t>
+          <t xml:space="preserve">SANKYO</t>
         </is>
       </c>
       <c r="E14">
-        <v>108.1</v>
-      </c>
-    </row>
-    <row r="15"/>
+        <v>97.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ ストリートファイター6</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">レオスター</t>
+        </is>
+      </c>
+      <c r="E15">
+        <v>97.4</v>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">設定6出率ランキング</t>
-        </is>
-      </c>
       <c r="B16">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">L ゴジラ対エヴァンゲリオン</t>
+          <t xml:space="preserve">Lすーぱぁびん娘</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビスティ</t>
+          <t xml:space="preserve">ベルコ</t>
         </is>
       </c>
       <c r="E16">
-        <v>114.9</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="17">
       <c r="B17">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">スマスロ モンキーターンV</t>
+          <t xml:space="preserve">マイジャグラーVI</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">山佐</t>
+          <t xml:space="preserve">北電子</t>
         </is>
       </c>
       <c r="E17">
-        <v>114.9</v>
+        <v>97.0</v>
       </c>
     </row>
     <row r="18">
       <c r="B18">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">スマスロ からくりサーカス</t>
+          <t xml:space="preserve">LBトリプルクラウンX-300</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">清龍ゲームジャパン</t>
+        </is>
+      </c>
+      <c r="E18">
+        <v>97.0</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">設定4出率ランキング</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ リコリス・リコイル</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t xml:space="preserve">サミー</t>
         </is>
       </c>
-      <c r="E18">
-        <v>114.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19">
-        <v>4</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lとある魔術の禁書目録2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">藤商事</t>
-        </is>
-      </c>
-      <c r="E19">
-        <v>113.3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20">
-        <v>5</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">スマスロ北斗の拳</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サミー</t>
-        </is>
-      </c>
       <c r="E20">
-        <v>113.0</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="21">
       <c r="B21">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">マイジャグラーV</t>
+          <t xml:space="preserve">L邪神ちゃんドロップキック</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">北電子</t>
+          <t xml:space="preserve">サンスリー</t>
         </is>
       </c>
       <c r="E21">
-        <v>109.4</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="22">
       <c r="B22">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ゴーゴージャグラー3</t>
+          <t xml:space="preserve">戦国コレクション6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">北電子</t>
+          <t xml:space="preserve">コナミアミューズメント</t>
         </is>
       </c>
       <c r="E22">
-        <v>106.5</v>
-      </c>
-    </row>
-    <row r="23"/>
+        <v>106.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ とんでもスキルで異世界放浪メシ</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コナミアミューズメント</t>
+        </is>
+      </c>
+      <c r="E23">
+        <v>105.3</v>
+      </c>
+    </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">設定1→設定6 出率差ランキング</t>
-        </is>
-      </c>
       <c r="B24">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">スマスロ からくりサーカス</t>
+          <t xml:space="preserve">スマスロ とある魔術の禁書目録2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">サミー</t>
+          <t xml:space="preserve">藤商事</t>
         </is>
       </c>
       <c r="E24">
-        <v>17.4</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="25">
       <c r="B25">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">L ゴジラ対エヴァンゲリオン</t>
+          <t xml:space="preserve">Lパチスロ 喰霊-零-Re</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビスティ</t>
+          <t xml:space="preserve">オーイズミ</t>
         </is>
       </c>
       <c r="E25">
-        <v>17.2</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="26">
       <c r="B26">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">スマスロ モンキーターンV</t>
+          <t xml:space="preserve">Lすーぱぁびん娘</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">山佐</t>
+          <t xml:space="preserve">ベルコ</t>
         </is>
       </c>
       <c r="E26">
-        <v>17.0</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="27">
       <c r="B27">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lとある魔術の禁書目録2</t>
+          <t xml:space="preserve">スマスロ ストリートファイター6</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">藤商事</t>
+          <t xml:space="preserve">レオスター</t>
         </is>
       </c>
       <c r="E27">
-        <v>15.4</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="28">
       <c r="B28">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">スマスロ北斗の拳</t>
+          <t xml:space="preserve">ローティス</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">北電子</t>
+        </is>
+      </c>
+      <c r="E28">
+        <v>102.7</v>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">設定5出率ランキング</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ リコリス・リコイル</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t xml:space="preserve">サミー</t>
         </is>
       </c>
-      <c r="E28">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29">
-        <v>6</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">マイジャグラーV</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">北電子</t>
-        </is>
-      </c>
-      <c r="E29">
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30">
-        <v>7</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ゴーゴージャグラー3</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">北電子</t>
-        </is>
-      </c>
       <c r="E30">
-        <v>9.3</v>
-      </c>
-    </row>
-    <row r="31"/>
+        <v>110.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31">
+        <v>2</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L邪神ちゃんドロップキック</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サンスリー</t>
+        </is>
+      </c>
+      <c r="E31">
+        <v>110.4</v>
+      </c>
+    </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コイン単価ランキング</t>
-        </is>
-      </c>
       <c r="B32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">L革命機ヴァルヴレイヴ</t>
+          <t xml:space="preserve">戦国コレクション6</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">不明</t>
+          <t xml:space="preserve">コナミアミューズメント</t>
         </is>
       </c>
       <c r="E32">
-        <v>4.5</v>
+        <v>110.1</v>
       </c>
     </row>
     <row r="33">
       <c r="B33">
+        <v>4</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ とんでもスキルで異世界放浪メシ</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コナミアミューズメント</t>
+        </is>
+      </c>
+      <c r="E33">
+        <v>109.1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34">
+        <v>5</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ とある魔術の禁書目録2</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">藤商事</t>
+        </is>
+      </c>
+      <c r="E34">
+        <v>108.2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35">
+        <v>6</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lすーぱぁびん娘</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベルコ</t>
+        </is>
+      </c>
+      <c r="E35">
+        <v>107.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36">
+        <v>7</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lパチスロ 喰霊-零-Re</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">オーイズミ</t>
+        </is>
+      </c>
+      <c r="E36">
+        <v>106.9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37">
+        <v>8</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ ストリートファイター6</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">レオスター</t>
+        </is>
+      </c>
+      <c r="E37">
+        <v>106.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38">
+        <v>9</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ローティス</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">北電子</t>
+        </is>
+      </c>
+      <c r="E38">
+        <v>105.0</v>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">設定6出率ランキング</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">パチスロ見える子ちゃん</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">パイオニア</t>
+        </is>
+      </c>
+      <c r="E40">
+        <v>114.9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41">
         <v>2</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">スマスロ北斗の拳</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lパチスロ 彼女、お借りします</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANKYO</t>
+        </is>
+      </c>
+      <c r="E41">
+        <v>114.9</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42">
+        <v>3</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">戦国コレクション6</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コナミアミューズメント</t>
+        </is>
+      </c>
+      <c r="E42">
+        <v>114.9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43">
+        <v>4</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ リコリス・リコイル</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t xml:space="preserve">サミー</t>
         </is>
       </c>
-      <c r="E33">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="34"/>
+      <c r="E43">
+        <v>114.6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44">
+        <v>5</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ 獣王</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サミー</t>
+        </is>
+      </c>
+      <c r="E44">
+        <v>114.3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45">
+        <v>6</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L邪神ちゃんドロップキック</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サンスリー</t>
+        </is>
+      </c>
+      <c r="E45">
+        <v>114.1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46">
+        <v>7</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ とある魔術の禁書目録2</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">藤商事</t>
+        </is>
+      </c>
+      <c r="E46">
+        <v>113.3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47">
+        <v>8</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lすーぱぁびん娘</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベルコ</t>
+        </is>
+      </c>
+      <c r="E47">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48">
+        <v>9</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スロット ワールドダイスター</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">パオン・ディーピー</t>
+        </is>
+      </c>
+      <c r="E48">
+        <v>112.4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49">
+        <v>10</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ とんでもスキルで異世界放浪メシ</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コナミアミューズメント</t>
+        </is>
+      </c>
+      <c r="E49">
+        <v>112.1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50">
+        <v>11</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L青春ブタ野郎はバニーガール先輩の夢を見ない</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">オリンピア</t>
+        </is>
+      </c>
+      <c r="E50">
+        <v>110.3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51">
+        <v>12</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lパチスロ 喰霊-零-Re</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">オーイズミ</t>
+        </is>
+      </c>
+      <c r="E51">
+        <v>110.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52">
+        <v>13</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ ストリートファイター6</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">レオスター</t>
+        </is>
+      </c>
+      <c r="E52">
+        <v>110.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53">
+        <v>14</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LBトリプルクラウンX-300</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">清龍ゲームジャパン</t>
+        </is>
+      </c>
+      <c r="E53">
+        <v>110.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54">
+        <v>15</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">マイジャグラーVI</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">北電子</t>
+        </is>
+      </c>
+      <c r="E54">
+        <v>109.4</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55">
+        <v>16</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ タコスロ</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ユニバーサルブロス</t>
+        </is>
+      </c>
+      <c r="E55">
+        <v>108.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56">
+        <v>17</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ローティス</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">北電子</t>
+        </is>
+      </c>
+      <c r="E56">
+        <v>108.1</v>
+      </c>
+    </row>
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">設定1→設定6 出率差ランキング</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lパチスロ 彼女、お借りします</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANKYO</t>
+        </is>
+      </c>
+      <c r="E58">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59">
+        <v>2</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">パチスロ見える子ちゃん</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">パイオニア</t>
+        </is>
+      </c>
+      <c r="E59">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60">
+        <v>3</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">戦国コレクション6</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コナミアミューズメント</t>
+        </is>
+      </c>
+      <c r="E60">
+        <v>17.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61">
+        <v>4</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ リコリス・リコイル</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サミー</t>
+        </is>
+      </c>
+      <c r="E61">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62">
+        <v>5</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ 獣王</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サミー</t>
+        </is>
+      </c>
+      <c r="E62">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63">
+        <v>6</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L邪神ちゃんドロップキック</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サンスリー</t>
+        </is>
+      </c>
+      <c r="E63">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64">
+        <v>7</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ とある魔術の禁書目録2</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">藤商事</t>
+        </is>
+      </c>
+      <c r="E64">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65">
+        <v>8</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lすーぱぁびん娘</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベルコ</t>
+        </is>
+      </c>
+      <c r="E65">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66">
+        <v>9</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スロット ワールドダイスター</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">パオン・ディーピー</t>
+        </is>
+      </c>
+      <c r="E66">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67">
+        <v>10</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ とんでもスキルで異世界放浪メシ</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コナミアミューズメント</t>
+        </is>
+      </c>
+      <c r="E67">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68">
+        <v>11</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LBトリプルクラウンX-300</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">清龍ゲームジャパン</t>
+        </is>
+      </c>
+      <c r="E68">
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69">
+        <v>12</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ ストリートファイター6</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">レオスター</t>
+        </is>
+      </c>
+      <c r="E69">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70">
+        <v>13</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">マイジャグラーVI</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">北電子</t>
+        </is>
+      </c>
+      <c r="E70">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71">
+        <v>14</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L青春ブタ野郎はバニーガール先輩の夢を見ない</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">オリンピア</t>
+        </is>
+      </c>
+      <c r="E71">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72">
+        <v>15</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lパチスロ 喰霊-零-Re</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">オーイズミ</t>
+        </is>
+      </c>
+      <c r="E72">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73">
+        <v>16</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ローティス</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">北電子</t>
+        </is>
+      </c>
+      <c r="E73">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74">
+        <v>17</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ タコスロ</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ユニバーサルブロス</t>
+        </is>
+      </c>
+      <c r="E74">
+        <v>9.8</v>
+      </c>
+    </row>
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コイン単価ランキング</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">該当データなし</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E34"/>
+  <autoFilter ref="A1:E76"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="45" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -1680,7 +2815,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">マイジャグラーV</t>
+          <t xml:space="preserve">マイジャグラーVI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1694,33 +2829,33 @@
         </is>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ コイン単価未確認 ／ 出率条件が不明</t>
+          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ コイン単価未確認 ／ 出率の情報源が1つしかない（照合未達） ／ 出率条件が不明 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://nana-press.com/post/1546517 | https://slobase.jp/machines/myjuggler5</t>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/5054</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">L ゴジラ対エヴァンゲリオン</t>
+          <t xml:space="preserve">スマスロ 獣王</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビスティ</t>
+          <t xml:space="preserve">サミー</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1729,133 +2864,138 @@
         </is>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ コイン単価未確認 ／ 出率条件が不明</t>
+          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ コイン単価未確認 ／ 出率の情報源が1つしかない（照合未達） ／ 出率条件が不明 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9990 | https://p-town.dmm.com/machines/4501</t>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/5061</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">スマスロ モンキーターンV</t>
+          <t xml:space="preserve">パチスロ見える子ちゃん</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">山佐</t>
+          <t xml:space="preserve">パイオニア</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">要確認</t>
+          <t xml:space="preserve">低</t>
         </is>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定5出率 ／ コイン単価未確認 ／ 出率条件が不明</t>
+          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ コイン単価未確認 ／ 出率の情報源が1つしかない（照合未達） ／ 出率条件が不明 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9923 | https://hazuse.com/machine/pachislot/3S0772/</t>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/5042</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">押忍!番長ZERO</t>
+          <t xml:space="preserve">スマスロ タコスロ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">大都技研</t>
+          <t xml:space="preserve">ユニバーサルブロス</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">要確認</t>
+          <t xml:space="preserve">低</t>
         </is>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定1〜6の出率が1つも入っていない（データ欠損） ／ コイン単価未確認 ／ 現行機かどうか不明（現行判定要確認）</t>
+          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ コイン単価未確認 ／ 出率の情報源が1つしかない（照合未達） ／ 出率条件が不明 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/5049</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">スマスロ からくりサーカス</t>
+          <t xml:space="preserve">L青春ブタ野郎はバニーガール先輩の夢を見ない</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">サミー</t>
+          <t xml:space="preserve">オリンピア</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">要確認</t>
+          <t xml:space="preserve">低</t>
         </is>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定4出率 ／ コイン単価未確認 ／ 出率条件が不明</t>
+          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ コイン単価未確認 ／ 出率の情報源が1つしかない（照合未達） ／ 出率条件が不明 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9843 | https://altema.jp/pachimo/lkarakuri</t>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/5064</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ゴーゴージャグラー3</t>
+          <t xml:space="preserve">Lパチスロ 彼女、お借りします</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">北電子</t>
+          <t xml:space="preserve">SANKYO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1864,63 +3004,68 @@
         </is>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ コイン単価未確認 ／ 出率条件が不明</t>
+          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ コイン単価未確認 ／ 出率の情報源が1つしかない（照合未達） ／ 出率条件が不明 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9848 | https://jugglersnet.com/analysis/gogo-juggler3</t>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/5065</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ニューハナハナゴールド-30</t>
+          <t xml:space="preserve">スロット ワールドダイスター</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">パイオニア</t>
+          <t xml:space="preserve">パオン・ディーピー</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">要確認</t>
+          <t xml:space="preserve">低</t>
         </is>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定1〜6の出率が1つも入っていない（データ欠損） ／ コイン単価未確認 ／ 現行機かどうか不明（現行判定要確認）</t>
+          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ コイン単価未確認 ／ 出率の情報源が1つしかない（照合未達） ／ 出率条件が不明 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/5055</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">スマスロ北斗の拳</t>
+          <t xml:space="preserve">LBトリプルクラウンX-300</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">サミー</t>
+          <t xml:space="preserve">清龍ゲームジャパン</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1929,91 +3074,431 @@
         </is>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ 出率条件が不明</t>
+          <t xml:space="preserve">出率欠損: 設定2出率, 設定3出率, 設定4出率, 設定5出率 ／ コイン単価未確認 ／ 出率の情報源が1つしかない（照合未達） ／ 出率条件が不明 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://p-town.dmm.com/machines/4301 | https://p.hisshobon.jp/vpage.php?c=2517&amp;p=2</t>
+          <t xml:space="preserve">https://p-town.dmm.com/machines/5089</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">L革命機ヴァルヴレイヴ</t>
+          <t xml:space="preserve">Lすーぱぁびん娘</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">不明</t>
+          <t xml:space="preserve">ベルコ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">要確認</t>
+          <t xml:space="preserve">高</t>
         </is>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定1〜6の出率が1つも入っていない（データ欠損） ／ メーカー不明</t>
+          <t xml:space="preserve">出率欠損: 設定3出率 ／ コイン単価未確認 ／ 出率条件が不明 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://slobase.jp/machines/super-bin-musume | https://p-town.dmm.com/machines/5038</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lとある魔術の禁書目録2</t>
+          <t xml:space="preserve">ローティス</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t xml:space="preserve">北電子</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出率欠損: 設定3出率 ／ コイン単価未確認 ／ 出率条件が不明 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://slobase.jp/machines/rotis | https://p-town.dmm.com/machines/5029</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロパリピ孔明</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">山佐</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">要確認</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">設定1〜6の出率が1つも入っていない（データ欠損） ／ コイン単価未確認 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L 転生王女と天才令嬢の魔法革命</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">オリンピアエステート</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">要確認</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">設定1〜6の出率が1つも入っていない（データ欠損） ／ コイン単価未確認 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">モグモグ風林火山 大海戦の巻</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ネット</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">要確認</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">設定1〜6の出率が1つも入っていない（データ欠損） ／ コイン単価未確認 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ リコリス・リコイル</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サミー</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コイン単価未確認 ／ 出率条件が不明 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://slobase.jp/machines/lycoris-recoil | https://p-town.dmm.com/machines/5033</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lパチスロ 喰霊-零-Re</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">オーイズミ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コイン単価未確認 ／ 出率条件が不明 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://slobase.jp/machines/garei-zero-re | https://p-town.dmm.com/machines/5028</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ ストリートファイター6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">レオスター</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コイン単価未確認 ／ 出率条件が不明 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://slobase.jp/machines/street-fighter6 | https://p-town.dmm.com/machines/5068</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ とんでもスキルで異世界放浪メシ</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コナミアミューズメント</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コイン単価未確認 ／ 出率条件が不明 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://slobase.jp/machines/tondemo-skill | https://p-town.dmm.com/machines/5030</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スマスロ とある魔術の禁書目録2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t xml:space="preserve">藤商事</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コイン単価未確認 ／ 出率条件が不明</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.slopachi-quest.com/article/toaru-majutsu-no-kinsho-mokuroku-2-settei/ | https://p-town.dmm.com/machines/5053</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-12</t>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コイン単価未確認 ／ 出率条件が不明 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://slobase.jp/machines/toaru-majutsu2 | https://p-town.dmm.com/machines/5053</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L邪神ちゃんドロップキック</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サンスリー</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コイン単価未確認 ／ 出率条件が不明 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://slobase.jp/machines/jashin-chan-dropkick | https://p-town.dmm.com/machines/5020</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">戦国コレクション6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コナミアミューズメント</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コイン単価未確認 ／ 出率条件が不明 ／ 現行機かどうか不明（現行判定要確認） ／ 機種タイプ不明</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://slobase.jp/machines/sengoku-collection6 | https://p-town.dmm.com/machines/5010</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G21"/>
 </worksheet>
 </file>
 
@@ -2022,11 +3507,11 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="49" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="52" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2065,27 +3550,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">押忍!番長ZERO</t>
+          <t xml:space="preserve">スマスロパリピ孔明</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">大都技研</t>
+          <t xml:space="preserve">山佐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">検索結果に機械割の数値記載がなく、一次ページ（ななプレス等）がegressブロックで開けない</t>
+          <t xml:space="preserve">設定別出率・機械割のいずれも掲載を確認できなかった</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">P-WORLD / DMMぱちタウン / ななプレス / ちょんぼりすた</t>
+          <t xml:space="preserve">DMMぱちタウン / P-WORLD</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9539</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10518 | https://p-town.dmm.com/machines/5057</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2097,27 +3582,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ニューハナハナゴールド-30</t>
+          <t xml:space="preserve">L 転生王女と天才令嬢の魔法革命</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パイオニア</t>
+          <t xml:space="preserve">オリンピアエステート</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検索結果に機械割の数値記載がなく、一次ページ（スロベース/P-WORLD）がegressブロックで開けない</t>
+          <t xml:space="preserve">設定別出率・機械割のいずれも掲載を確認できなかった</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">P-WORLD / DMMぱちタウン / スロベース / 一撃</t>
+          <t xml:space="preserve">DMMぱちタウン / P-WORLD</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9267</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10550 | https://p-town.dmm.com/machines/5086</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2129,27 +3614,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">L革命機ヴァルヴレイヴ</t>
+          <t xml:space="preserve">モグモグ風林火山 大海戦の巻</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">不明</t>
+          <t xml:space="preserve">ネット</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">検索結果に機械割の数値記載なし。メーカーも一次情報未確認</t>
+          <t xml:space="preserve">設定別出率・機械割のいずれも掲載を確認できなかった</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">P-WORLD / アルテマ / 一撃 / ちょんぼりすた</t>
+          <t xml:space="preserve">DMMぱちタウン / P-WORLD</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/9725</t>
+          <t xml:space="preserve">https://www.p-world.co.jp/machine/database/10523 | https://p-town.dmm.com/machines/5059</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
